--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/CALIFORNIA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/CALIFORNIA_2012.xlsx
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C197">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C262">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C296">
@@ -10381,7 +10381,7 @@
         <v>316</v>
       </c>
       <c r="D557">
-        <v>0.00092686017317</v>
+        <v>0.0009268601731700002</v>
       </c>
     </row>
     <row r="558">
@@ -12919,7 +12919,7 @@
         <v>334</v>
       </c>
       <c r="D698">
-        <v>0.000979656005819</v>
+        <v>0.0009796560058190002</v>
       </c>
     </row>
     <row r="699">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C918">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1143">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1144">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1245">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1246">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1259">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1435">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1549">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="B1916" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1916">
@@ -35790,7 +35790,7 @@
       </c>
       <c r="B1969" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1969">
@@ -39192,7 +39192,7 @@
       </c>
       <c r="B2158" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C2158">
